--- a/media/files_for_bulk_import_of_ads/admin@super.com/error_admin@super.com.xlsx
+++ b/media/files_for_bulk_import_of_ads/admin@super.com/error_admin@super.com.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="48">
   <si>
     <t>заголовок</t>
   </si>
@@ -64,79 +64,100 @@
     <t>фото1</t>
   </si>
   <si>
+    <t>фото2</t>
+  </si>
+  <si>
+    <t>Ленинский район</t>
+  </si>
+  <si>
+    <t>Автомобили с пробегом</t>
+  </si>
+  <si>
+    <t>Citroen C15</t>
+  </si>
+  <si>
+    <t>битый</t>
+  </si>
+  <si>
+    <t>механика</t>
+  </si>
+  <si>
+    <t>красный</t>
+  </si>
+  <si>
+    <t>бензин</t>
+  </si>
+  <si>
+    <t>хетчбэк</t>
+  </si>
+  <si>
+    <t>трулюлюл</t>
+  </si>
+  <si>
+    <t>1255568АО</t>
+  </si>
+  <si>
+    <t>kvartira_1.jpg</t>
+  </si>
+  <si>
+    <t>kvartira.jpg</t>
+  </si>
+  <si>
     <t>Барановичи</t>
   </si>
   <si>
-    <t>Автомобили с пробегом</t>
-  </si>
-  <si>
     <t>BMW X5</t>
   </si>
   <si>
+    <t>2550000,5</t>
+  </si>
+  <si>
     <t>среднее</t>
   </si>
   <si>
-    <t>механика</t>
-  </si>
-  <si>
     <t>белый</t>
   </si>
   <si>
-    <t>бензин</t>
-  </si>
-  <si>
     <t>кроссовер</t>
   </si>
   <si>
     <t>траляляля</t>
   </si>
   <si>
-    <t>1231568АО</t>
+    <t>1255571АО</t>
   </si>
   <si>
     <t>enot_1.png</t>
   </si>
   <si>
-    <t>Ленинский район</t>
-  </si>
-  <si>
-    <t>Citroen C15</t>
-  </si>
-  <si>
-    <t>битый</t>
-  </si>
-  <si>
-    <t>красный</t>
-  </si>
-  <si>
-    <t>хетчбэк</t>
-  </si>
-  <si>
-    <t>трулюлюл</t>
-  </si>
-  <si>
-    <t>1255568АО</t>
-  </si>
-  <si>
-    <t>kvartira_1.jpg</t>
-  </si>
-  <si>
-    <t>фото2</t>
-  </si>
-  <si>
-    <t>kvartira_2.jpg</t>
-  </si>
-  <si>
-    <t>error</t>
-  </si>
-  <si>
-    <t>траояояо</t>
-  </si>
-  <si>
-    <t>123858АО</t>
-  </si>
-  <si>
-    <t>ww.png</t>
+    <t>мех</t>
+  </si>
+  <si>
+    <t>1255573АО</t>
+  </si>
+  <si>
+    <t>Автомобили</t>
+  </si>
+  <si>
+    <t>1255575АО</t>
+  </si>
+  <si>
+    <t>1255577АО</t>
+  </si>
+  <si>
+    <t>1255581АО</t>
+  </si>
+  <si>
+    <t>1255583АО</t>
+  </si>
+  <si>
+    <t>enot.png</t>
+  </si>
+  <si>
+    <t>Фиг знает где</t>
+  </si>
+  <si>
+    <t>1255585АО</t>
   </si>
 </sst>
 </file>
@@ -468,7 +489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -521,160 +542,407 @@
         <v>15</v>
       </c>
       <c r="Q1" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2">
-        <v>1111</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2">
-        <v>2550000</v>
+        <v>30000.25</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2">
-        <v>128000</v>
+        <v>220000</v>
       </c>
       <c r="J2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="N2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P2" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:17">
       <c r="A3">
-        <v>2222</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3">
-        <v>30000.25</v>
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>31</v>
       </c>
       <c r="F3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="H3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3">
-        <v>220000</v>
+        <v>128000</v>
       </c>
       <c r="J3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M3">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="N3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="O3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:17">
-      <c r="A4" t="s">
-        <v>37</v>
+      <c r="A4">
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E4">
         <v>2550000</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G4">
         <v>2007</v>
       </c>
       <c r="H4" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="I4">
         <v>128000</v>
       </c>
       <c r="J4" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="K4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L4" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="M4">
         <v>5</v>
       </c>
       <c r="N4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="O4" t="s">
         <v>39</v>
       </c>
       <c r="P4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
         <v>40</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5">
+        <v>2550000</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5">
+        <v>2007</v>
+      </c>
+      <c r="H5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5">
+        <v>128000</v>
+      </c>
+      <c r="J5" t="s">
+        <v>33</v>
+      </c>
+      <c r="K5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L5" t="s">
+        <v>34</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
+      </c>
+      <c r="N5" t="s">
+        <v>35</v>
+      </c>
+      <c r="O5" t="s">
+        <v>41</v>
+      </c>
+      <c r="P5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6">
+        <v>30000.25</v>
+      </c>
+      <c r="F6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6">
+        <v>2005</v>
+      </c>
+      <c r="H6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6">
+        <v>220000</v>
+      </c>
+      <c r="J6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M6">
+        <v>2.4</v>
+      </c>
+      <c r="N6" t="s">
+        <v>25</v>
+      </c>
+      <c r="O6" t="s">
+        <v>42</v>
+      </c>
+      <c r="P6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7">
+        <v>2550000</v>
+      </c>
+      <c r="F7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7">
+        <v>2007</v>
+      </c>
+      <c r="H7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7">
+        <v>128000</v>
+      </c>
+      <c r="J7" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M7">
+        <v>5</v>
+      </c>
+      <c r="O7" t="s">
+        <v>43</v>
+      </c>
+      <c r="P7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8">
+        <v>2550000</v>
+      </c>
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8">
+        <v>2007</v>
+      </c>
+      <c r="H8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8">
+        <v>128000</v>
+      </c>
+      <c r="J8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8" t="s">
+        <v>23</v>
+      </c>
+      <c r="L8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M8">
+        <v>5</v>
+      </c>
+      <c r="N8" t="s">
+        <v>35</v>
+      </c>
+      <c r="O8" t="s">
+        <v>44</v>
+      </c>
+      <c r="P8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9">
+        <v>2550000</v>
+      </c>
+      <c r="F9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9">
+        <v>2007</v>
+      </c>
+      <c r="H9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9">
+        <v>128000</v>
+      </c>
+      <c r="J9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M9">
+        <v>5</v>
+      </c>
+      <c r="N9" t="s">
+        <v>35</v>
+      </c>
+      <c r="O9" t="s">
+        <v>47</v>
+      </c>
+      <c r="P9" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
